--- a/utils/monday_sprint_sprint_2024-30.xlsx
+++ b/utils/monday_sprint_sprint_2024-30.xlsx
@@ -366,7 +366,7 @@
     <t>17/03/2023</t>
   </si>
   <si>
-    <t>09/05/2026</t>
+    <t>04/05/2026</t>
   </si>
   <si>
     <t>Março</t>
@@ -3239,7 +3239,7 @@
         <v>33</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3271,7 +3271,7 @@
         <v>42</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3385,7 +3385,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>112</v>
@@ -3399,7 +3399,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>122</v>
@@ -3413,7 +3413,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>127</v>

--- a/utils/monday_sprint_sprint_2024-30.xlsx
+++ b/utils/monday_sprint_sprint_2024-30.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="181">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -87,7 +87,7 @@
     <t>19/02/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>03/03/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -111,7 +111,7 @@
     <t>6092432593</t>
   </si>
   <si>
-    <t>24768</t>
+    <t>6144569175</t>
   </si>
   <si>
     <t>Apontamentos Moldagem UPR FEV/2024</t>
@@ -123,10 +123,13 @@
     <t>27/02/2024</t>
   </si>
   <si>
+    <t>26/02/2024</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>24106</t>
+    <t>5893378185</t>
   </si>
   <si>
     <t>Colocar cód de barras no romaneio</t>
@@ -135,10 +138,13 @@
     <t>19/01/2024</t>
   </si>
   <si>
+    <t>29/02/2024</t>
+  </si>
+  <si>
     <t>Janeiro</t>
   </si>
   <si>
-    <t>24265</t>
+    <t>5990586571</t>
   </si>
   <si>
     <t>Melhoria Registro Moldagem USE/ULE</t>
@@ -150,25 +156,25 @@
     <t>Semana 1</t>
   </si>
   <si>
-    <t>24397</t>
+    <t>5989779431</t>
   </si>
   <si>
     <t>Registro de contaminação da suspensão de PM</t>
   </si>
   <si>
-    <t>24329</t>
+    <t>5990704333</t>
   </si>
   <si>
     <t>LIBERAR ACESSO PARA REALIZAR INVENTÁRIO GERAL</t>
   </si>
   <si>
-    <t>24334</t>
+    <t>5990066012</t>
   </si>
   <si>
     <t>CONSULTA SALDO DEPÓSITO</t>
   </si>
   <si>
-    <t>24403</t>
+    <t>6034774433</t>
   </si>
   <si>
     <t>Relat de conclusão de Pré Usin e Usin Final no planilhão</t>
@@ -180,7 +186,7 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>23458</t>
+    <t>5894539074</t>
   </si>
   <si>
     <t>Retorno para o NIMBI ao entrar a NF quando recebida</t>
@@ -189,7 +195,7 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>24530</t>
+    <t>6080671131</t>
   </si>
   <si>
     <t>Tela de A.C - Documentos Anexos (AP119)</t>
@@ -198,31 +204,40 @@
     <t>16/02/2024</t>
   </si>
   <si>
-    <t>24352</t>
+    <t>20/02/2024</t>
+  </si>
+  <si>
+    <t>5989948868</t>
   </si>
   <si>
     <t>Erro no sistema de apontamento de Solda - 13649</t>
   </si>
   <si>
-    <t>24529</t>
+    <t>6080846298</t>
   </si>
   <si>
     <t>Tela OTF - Desenhos</t>
   </si>
   <si>
-    <t>24626</t>
+    <t>6080283934</t>
   </si>
   <si>
     <t>TICKET SETOR 595</t>
   </si>
   <si>
-    <t>24521</t>
+    <t>02/03/2024</t>
+  </si>
+  <si>
+    <t>6080862976</t>
   </si>
   <si>
     <t>Inclusão de Numero de Invoice - Rel NF</t>
   </si>
   <si>
-    <t>24623</t>
+    <t>21/02/2024</t>
+  </si>
+  <si>
+    <t>6080292856</t>
   </si>
   <si>
     <t>Criação tela de geração OC por XML Sistema Compras</t>
@@ -231,19 +246,22 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>24520</t>
+    <t>25/02/2024</t>
+  </si>
+  <si>
+    <t>6080962991</t>
   </si>
   <si>
     <t>Relatório de PM</t>
   </si>
   <si>
-    <t>24606</t>
+    <t>6080331344</t>
   </si>
   <si>
     <t>Informações complementares</t>
   </si>
   <si>
-    <t>24594</t>
+    <t>6080407316</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -252,136 +270,139 @@
     <t>Portal de pendencias II</t>
   </si>
   <si>
-    <t>24489</t>
+    <t>6034647871</t>
   </si>
   <si>
     <t>Habilitação do setor 2088 para ToTo</t>
   </si>
   <si>
-    <t>24582</t>
+    <t>6080427209</t>
   </si>
   <si>
     <t>Apontamento ajustagem</t>
   </si>
   <si>
-    <t>24476</t>
+    <t>28/02/2024</t>
+  </si>
+  <si>
+    <t>6034679254</t>
   </si>
   <si>
     <t>Consistência de fase de projeto na SIC</t>
   </si>
   <si>
-    <t>24578</t>
+    <t>6080503619</t>
   </si>
   <si>
     <t>Previsão de Vendas QSense - Adicionar Campo</t>
   </si>
   <si>
-    <t>24609</t>
+    <t>6080318455</t>
   </si>
   <si>
     <t>Portal de pendencias</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>6090760964</t>
   </si>
   <si>
     <t>Acompanhamento Produtivo em Horas</t>
   </si>
   <si>
-    <t>24574</t>
+    <t>6080512431</t>
   </si>
   <si>
     <t>Adicionar nome do cliente no relatório estatística mensais (movimentação)</t>
   </si>
   <si>
-    <t>24571</t>
+    <t>6080529728</t>
   </si>
   <si>
     <t>Relatório blocos de prova</t>
   </si>
   <si>
-    <t>24637</t>
+    <t>6091910222</t>
   </si>
   <si>
     <t>Imposto de Importação - Somar no total da NF</t>
   </si>
   <si>
-    <t>24425</t>
+    <t>6034724730</t>
   </si>
   <si>
     <t>Geração de planilha Excel</t>
   </si>
   <si>
-    <t>24564</t>
+    <t>22/02/2024</t>
+  </si>
+  <si>
+    <t>6080558420</t>
   </si>
   <si>
     <t>Melhoria - Portal de pendencias</t>
   </si>
   <si>
-    <t>24424</t>
+    <t>6034732939</t>
   </si>
   <si>
     <t>Verificação automática de CTes</t>
   </si>
   <si>
-    <t>24569</t>
+    <t>6080541124</t>
   </si>
   <si>
     <t>Melhoria portal de pendências compras x fiscal</t>
   </si>
   <si>
-    <t>24557</t>
+    <t>6080569849</t>
   </si>
   <si>
     <t>Alteração do apontamento</t>
   </si>
   <si>
-    <t>24423</t>
+    <t>6034742230</t>
   </si>
   <si>
     <t>[ALTONA] Cadastro de tipo de frete N/A</t>
   </si>
   <si>
-    <t>24547</t>
+    <t>6080618603</t>
   </si>
   <si>
     <t>Pré-embarque</t>
   </si>
   <si>
-    <t>24642</t>
+    <t>6093361413</t>
   </si>
   <si>
     <t>Erro no apontamento de ajustagem</t>
   </si>
   <si>
-    <t>24715</t>
+    <t>6111437581</t>
   </si>
   <si>
     <t>Apontamento da ajustagem -  Mensagem de que esta sendo adicionado um modelo diferente</t>
   </si>
   <si>
-    <t>21/02/2024</t>
-  </si>
-  <si>
-    <t>24709</t>
+    <t>6110047360</t>
   </si>
   <si>
     <t>cálculo da razão crítica</t>
   </si>
   <si>
-    <t>24695</t>
+    <t>6110072688</t>
   </si>
   <si>
     <t>Base de Cálculo ICMS - NF de importação</t>
   </si>
   <si>
-    <t>24519</t>
+    <t>6080989337</t>
   </si>
   <si>
     <t>Relatório Peso por Área</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>6073940857</t>
   </si>
   <si>
     <t>Sistema Novo de Revisão de Documentos - Sprint 4/4 - Análise</t>
@@ -414,7 +435,7 @@
     <t>04/05/2026</t>
   </si>
   <si>
-    <t>21601</t>
+    <t>6090517988</t>
   </si>
   <si>
     <t>GERAÇÃO DE ROMANEIO - EXPEDIÇÃO - ANÁLISE</t>
@@ -438,7 +459,7 @@
     <t>Consulta cadastro de caixas.</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>6144538930</t>
   </si>
   <si>
     <t>Critério para seleção de apontamentos UPR (1210 - Carrosssel e 1296 - Fast Loop)</t>
@@ -450,7 +471,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-30</t>
+    <t>Jan/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -517,6 +538,9 @@
   </si>
   <si>
     <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -1186,7 +1210,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1195,7 +1219,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1203,7 +1227,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1215,10 +1239,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -1230,10 +1254,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1245,12 +1269,12 @@
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1262,10 +1286,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -1277,10 +1301,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1289,7 +1313,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1297,7 +1321,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1309,10 +1333,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -1324,10 +1348,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1336,7 +1360,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1344,7 +1368,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1356,10 +1380,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -1371,10 +1395,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1383,7 +1407,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1391,7 +1415,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1403,10 +1427,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -1418,10 +1442,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1430,7 +1454,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1438,7 +1462,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1450,10 +1474,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -1465,10 +1489,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1477,7 +1501,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1485,7 +1509,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1497,13 +1521,13 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>21</v>
@@ -1512,10 +1536,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1527,12 +1551,12 @@
         <v>27</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1544,10 +1568,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -1559,10 +1583,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1579,7 +1603,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1591,13 +1615,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>21</v>
@@ -1606,10 +1630,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1618,7 +1642,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1626,7 +1650,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1638,10 +1662,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -1653,10 +1677,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1673,7 +1697,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1685,10 +1709,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -1700,10 +1724,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1720,7 +1744,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1732,10 +1756,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -1747,10 +1771,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1767,7 +1791,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1779,13 +1803,13 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1794,10 +1818,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1814,7 +1838,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1826,13 +1850,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -1841,10 +1865,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1861,7 +1885,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1873,10 +1897,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -1888,10 +1912,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1908,22 +1932,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -1935,10 +1959,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1955,7 +1979,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1967,10 +1991,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -1982,10 +2006,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1994,7 +2018,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -2002,7 +2026,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2014,10 +2038,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -2029,10 +2053,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2049,7 +2073,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2061,10 +2085,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -2076,10 +2100,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2088,7 +2112,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2096,7 +2120,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2108,10 +2132,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -2123,10 +2147,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2143,22 +2167,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -2170,10 +2194,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2190,22 +2214,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -2220,7 +2244,7 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2237,7 +2261,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2249,10 +2273,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -2264,10 +2288,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2284,7 +2308,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2296,10 +2320,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -2311,10 +2335,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2331,7 +2355,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2343,10 +2367,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -2361,7 +2385,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2378,7 +2402,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2390,13 +2414,13 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2405,10 +2429,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2417,7 +2441,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2425,7 +2449,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2437,10 +2461,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -2452,10 +2476,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2472,22 +2496,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -2499,10 +2523,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2511,7 +2535,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2519,7 +2543,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2531,10 +2555,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -2546,10 +2570,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2566,7 +2590,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2578,10 +2602,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>34</v>
@@ -2593,10 +2617,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2613,7 +2637,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2625,10 +2649,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
@@ -2640,10 +2664,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2652,7 +2676,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2660,7 +2684,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2672,13 +2696,13 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>21</v>
@@ -2687,10 +2711,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2707,7 +2731,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2719,10 +2743,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>34</v>
@@ -2737,7 +2761,7 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2754,7 +2778,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2766,13 +2790,13 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>21</v>
@@ -2781,10 +2805,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2801,7 +2825,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2813,10 +2837,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>34</v>
@@ -2828,10 +2852,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2848,7 +2872,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2860,10 +2884,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2875,10 +2899,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2895,7 +2919,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2907,10 +2931,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>34</v>
@@ -2922,10 +2946,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2942,22 +2966,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>34</v>
@@ -2969,10 +2993,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2989,37 +3013,37 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3036,25 +3060,25 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>21</v>
@@ -3066,7 +3090,7 @@
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3083,37 +3107,37 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3130,37 +3154,37 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3177,7 +3201,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3189,10 +3213,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>34</v>
@@ -3207,7 +3231,7 @@
         <v>35</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3216,7 +3240,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -3235,23 +3259,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3259,16 +3283,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3279,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>806</v>
+        <v>29.79</v>
       </c>
       <c r="J5" s="4">
         <v>3</v>
@@ -3287,7 +3311,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3300,7 +3324,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3308,7 +3332,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3339,12 +3363,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B2">
         <v>47</v>
@@ -3358,7 +3382,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>806</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3368,25 +3392,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3403,13 +3427,13 @@
         <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3421,27 +3445,27 @@
         <v>47</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -3453,21 +3477,21 @@
         <v>47</v>
       </c>
       <c r="M11" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -3485,42 +3509,42 @@
         <v>35</v>
       </c>
       <c r="J12" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="Q12">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
@@ -3531,7 +3555,7 @@
         <v>4</v>
       </c>
       <c r="M14" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3539,7 +3563,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3547,7 +3571,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3555,7 +3579,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3563,10 +3587,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3574,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3582,16 +3606,16 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F21" s="2">
-        <v>791</v>
+        <v>823</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3602,7 +3626,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -3616,7 +3640,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -3630,7 +3654,7 @@
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -3638,86 +3662,86 @@
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
